--- a/pipeline/credit_rating/output/visrating_xhtn_20260920.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260920.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:45</t>
+          <t>2026-09-20 13:11:35</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
